--- a/product family/MX150/MX150 2X10 RCPT (33472)/Reference Numbers.xlsx
+++ b/product family/MX150/MX150 2X10 RCPT (33472)/Reference Numbers.xlsx
@@ -564,11 +564,6 @@
           <t>Polarity-A,Color-BLACK,CPA-N,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -635,11 +630,6 @@
           <t>Polarity-A,Color-BLACK,CPA-Y,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -706,11 +696,6 @@
           <t>Polarity-B,Color-LIGHT GRAY,CPA-N,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -777,11 +762,6 @@
           <t>Polarity-B,Color-LIGHT GRAY,CPA-Y,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -848,11 +828,6 @@
           <t>Polarity-C,Color-DARK GRAY,CPA-N,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -919,11 +894,6 @@
           <t>Polarity-C,Color-DARK GRAY,CPA-Y,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -990,11 +960,6 @@
           <t>Polarity-D,Color-STONE GRAY,CPA-N,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1061,11 +1026,6 @@
           <t>Polarity-D,Color-STONE GRAY,CPA-Y,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1132,11 +1092,6 @@
           <t>Polarity-A,Color-BLACK,CPA-N,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1203,11 +1158,6 @@
           <t>Polarity-A,Color-BLACK,CPA-Y,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1274,11 +1224,6 @@
           <t>Polarity-B,Color-LIGHT GRAY,CPA-N,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1345,11 +1290,6 @@
           <t>Polarity-B,Color-LIGHT GRAY,CPA-Y,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1416,11 +1356,6 @@
           <t>Polarity-C,Color-DARK GRAY,CPA-N,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1487,11 +1422,6 @@
           <t>Polarity-C,Color-DARK GRAY,CPA-Y,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1558,11 +1488,6 @@
           <t>Polarity-D,Color-STONE GRAY,CPA-N,Clipslot-Y,Grommet Cap-STANDARD</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1627,11 +1552,6 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>Polarity-D,Color-STONE GRAY,CPA-Y,Clipslot-Y,Grommet Cap-STANDARD</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>BACKSHELL WITH RIBS-34951-2011,BACKSHELL WITHOUT RIBS-34951-2021,90° ADAPTOR WITH RIBS-34951-1631,90° ADAPTOR WITHOUT RIBS-34951-1641</t>
         </is>
       </c>
     </row>
